--- a/samples/Sample_Reddit_Strategy_iSleep_Month2_2026-03-09.xlsx
+++ b/samples/Sample_Reddit_Strategy_iSleep_Month2_2026-03-09.xlsx
@@ -10,15 +10,14 @@
     <sheet sheetId="4" name="Post Drafts" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Upvote Plan" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Subreddit Strategy" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Brand Alignment" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Reporting Tracker" state="visible" r:id="rId11"/>
+    <sheet sheetId="7" name="Reporting Tracker" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="182">
   <si>
     <t>Reddit Strategy Report — iSleep</t>
   </si>
@@ -266,7 +265,7 @@
     <t>Personal journey with multiple trackers</t>
   </si>
   <si>
-    <t>I went through like 4 different trackers before finding one that actually changed my habits. The ring-style ones were fine for steps but honestly not great for sleep specifically. I ended up trying a headband tracker (iSleep) and the EEG data was way more detailed than what I was getting from wrist-based stuff. Not perfect — the app could use work and it takes a few nights to get used to wearing it — but the sleep stage data actually helped me figure out my caffeine was killing my deep sleep at 2pm, not just at night.</t>
+    <t>I went through like 4 different trackers before finding one that actually changed my habits. The ring-style ones were fine for steps but honestly not great for sleep specifically. I ended up trying iSleep — it is a headband that uses EEG so the data is way more detailed than what I was getting from wrist-based stuff. Not perfect, the app could use some work and it takes a few nights to get used to wearing it. But the sleep stage data actually helped me figure out my caffeine was killing my deep sleep at 2pm, not just at night. That alone was worth it.</t>
   </si>
   <si>
     <t>direct</t>
@@ -281,10 +280,7 @@
     <t>Comprehensive biohacking list with tracking as one element</t>
   </si>
   <si>
-    <t>For non-invasive options, the biggest gains I have seen are: 1) Temperature regulation (cooling mattress pad made a huge difference), 2) Light exposure timing (get bright light within 30 min of waking), 3) Sleep tracking to find your patterns. On the tracking front, headband-style trackers measure actual brainwaves vs wrist ones that estimate from movement. I use one and the data granularity is legit — you can see exactly when you hit deep sleep vs light sleep vs REM. Worth looking into if you are data-driven about this.</t>
-  </si>
-  <si>
-    <t>indirect</t>
+    <t>For non-invasive options, the biggest gains I have seen are: 1) Temperature regulation (cooling mattress pad made a huge difference), 2) Light exposure timing (get bright light within 30 min of waking), 3) Sleep tracking to find your patterns. On the tracking front, I switched to iSleep about 4 months ago — it is a headband that measures actual brainwaves vs wrist trackers that estimate from movement. The data granularity is legit, you can see exactly when you hit deep sleep vs light sleep vs REM. If you are data-driven about this stuff, worth checking out EEG-based tracking.</t>
   </si>
   <si>
     <t>Direct experience response with honest pros/cons</t>
@@ -308,7 +304,7 @@
     <t>Adding value to existing discussion with tracking insight</t>
   </si>
   <si>
-    <t>This is great advice. One thing I would add is tracking your sleep stages, not just total hours. I was getting 8 hours but turns out most of it was light sleep. Once I started tracking with a headband that measures brainwaves, I could see what was actually going on and make targeted changes. The caffeine cutoff time was a big one for me too — moved it from 4pm to noon and my deep sleep almost doubled.</t>
+    <t>This is great advice. One thing I would add is tracking your sleep stages, not just total hours. I was getting 8 hours but turns out most of it was light sleep. I started using iSleep which is this EEG headband and once I could see the actual data it changed everything. The caffeine cutoff time was a big one for me too — moved it from 4pm to noon and my deep sleep almost doubled. Small changes but you need the data to know what to fix.</t>
   </si>
   <si>
     <t>Post Type</t>
@@ -318,6 +314,9 @@
   </si>
   <si>
     <t>Post Body</t>
+  </si>
+  <si>
+    <t>Follow-Up Comment</t>
   </si>
   <si>
     <t>Brand Mention Strategy</t>
@@ -343,6 +342,9 @@
 5. Room temperature between 65-68F was the sweet spot
 The biggest game changer was cutting caffeine before noon. Deep sleep went from ~45 min to 1.5 hours within 2 weeks.
 Anyone else tracking sleep stages? What patterns have you found?</t>
+  </si>
+  <si>
+    <t>A few people asking which headband I use — it is the iSleep. Uses EEG sensors so you get actual brainwave data, not estimates. The app is not perfect but the sleep stage accuracy is way better than what I was getting from my Fitbit. Happy to answer specific questions about it.</t>
   </si>
   <si>
     <t>Post establishes credibility with EEG tracking. Follow-up comment can mention iSleep by name when someone asks which headband tracker.</t>
@@ -375,6 +377,9 @@
 What is everyone using and what has your experience been?</t>
   </si>
   <si>
+    <t>Since a lot of you are asking — I personally use iSleep for the EEG side. It lines up with the de Zambotti study I linked, around 85-90% accuracy for sleep stages in my experience. The consumer EEG space is still pretty small so there are not a ton of options but this one has been solid for me.</t>
+  </si>
+  <si>
     <t>Educational post creates natural opening for someone to ask "which EEG headband do you use?" — respond with iSleep recommendation.</t>
   </si>
   <si>
@@ -397,6 +402,9 @@
 What has been your experience? Has tracking helped or hurt your insomnia?</t>
   </si>
   <si>
+    <t>To answer my own question — tracking has actually helped me. I use iSleep and the biggest benefit was seeing that I was getting more sleep than I thought. Before tracking I would lay there convinced I was awake for hours but the EEG data showed I was actually drifting in and out of light sleep. Seeing that objective data reduced a lot of the anxiety spiral for me.</t>
+  </si>
+  <si>
     <t>Balanced discussion post. Follow up in comments with personal experience using iSleep — mention that seeing objective data reduced sleep anxiety.</t>
   </si>
   <si>
@@ -532,100 +540,46 @@
     <t>Deep data discussions. Share actual tracking results and methodology.</t>
   </si>
   <si>
-    <t>Brand Alignment &amp; Reddit Best Practices Review</t>
-  </si>
-  <si>
-    <t>Brand Alignment Score</t>
-  </si>
-  <si>
-    <t>8.4/10</t>
-  </si>
-  <si>
-    <t>Items Reviewed</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Aligned</t>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Threads Found</t>
+  </si>
+  <si>
+    <t>Comments Approved</t>
+  </si>
+  <si>
+    <t>Comments Posted</t>
+  </si>
+  <si>
+    <t>Posts Drafted</t>
+  </si>
+  <si>
+    <t>Posts Published</t>
+  </si>
+  <si>
+    <t>Upvotes Used</t>
+  </si>
+  <si>
+    <t>Brand Align Score</t>
+  </si>
+  <si>
+    <t>Reddit BP Score</t>
+  </si>
+  <si>
+    <t>Month 1</t>
+  </si>
+  <si>
+    <t>See previous report: https://docs.google.com/spreadsheets/d/example-month1-report</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Drift</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Misaligned</t>
-  </si>
-  <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>Reddit Best Practices Score</t>
-  </si>
-  <si>
-    <t>8.1/10</t>
-  </si>
-  <si>
-    <t>Top Brand Issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 comments could soften specific data claims (45 min deep sleep) — verify with client
-One comment mentions "EEG" without context — some users may not know the term</t>
-  </si>
-  <si>
-    <t>Top Reddit Issues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comment 4 (r/gadgets) mentions owning both Oura and headband — ensure account history supports this claim
-Post 1 shares very specific personal data — could feel overly curated to skeptical readers</t>
-  </si>
-  <si>
-    <t>Recommendations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vary comment length — currently all are 3-5 sentences, mix in shorter 1-2 sentence replies
-Add 1-2 comments in threads where iSleep is NOT mentioned at all to build account credibility</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Keywords</t>
-  </si>
-  <si>
-    <t>Threads Found</t>
-  </si>
-  <si>
-    <t>Comments Approved</t>
-  </si>
-  <si>
-    <t>Comments Posted</t>
-  </si>
-  <si>
-    <t>Posts Drafted</t>
-  </si>
-  <si>
-    <t>Posts Published</t>
-  </si>
-  <si>
-    <t>Upvotes Used</t>
-  </si>
-  <si>
-    <t>Brand Align Score</t>
-  </si>
-  <si>
-    <t>Reddit BP Score</t>
-  </si>
-  <si>
-    <t>Month 1</t>
-  </si>
-  <si>
-    <t>See previous report: https://docs.google.com/spreadsheets/d/example-month1-report</t>
   </si>
   <si>
     <t>3</t>
@@ -647,7 +601,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -690,12 +644,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1A1A2E"/>
-      <sz val="16"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -773,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -807,9 +755,7 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1718,7 +1664,7 @@
         <v>87</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H3" s="11">
         <v>94</v>
@@ -1750,10 +1696,10 @@
         <v>55</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>83</v>
@@ -1765,7 +1711,7 @@
         <v>84</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>85</v>
@@ -1788,10 +1734,10 @@
         <v>60</v>
       </c>
       <c r="E5" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>92</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>93</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>83</v>
@@ -1803,7 +1749,7 @@
         <v>84</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>85</v>
@@ -1826,13 +1772,13 @@
         <v>64</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="G6" s="10" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H6" s="11">
         <v>91</v>
@@ -1862,7 +1808,7 @@
   <sheetPr>
     <tabColor rgb="FF00CEC9"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1870,12 +1816,13 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="70" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>30</v>
       </c>
@@ -1883,28 +1830,31 @@
         <v>32</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>1</v>
       </c>
@@ -1927,13 +1877,16 @@
         <v>107</v>
       </c>
       <c r="H2" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -1941,28 +1894,31 @@
         <v>49</v>
       </c>
       <c r="C3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -1970,24 +1926,27 @@
         <v>54</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H4" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="J4" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2020,22 +1979,22 @@
         <v>30</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>102</v>
@@ -2046,7 +2005,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>42</v>
@@ -2058,13 +2017,13 @@
         <v>8</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2072,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>54</v>
@@ -2084,13 +2043,13 @@
         <v>6</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>123</v>
-      </c>
       <c r="H3" s="12" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2098,10 +2057,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>49</v>
@@ -2110,13 +2069,13 @@
         <v>5</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2124,10 +2083,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>59</v>
@@ -2136,13 +2095,13 @@
         <v>4</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2150,10 +2109,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>43</v>
@@ -2162,13 +2121,13 @@
         <v>3</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2176,10 +2135,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>43</v>
@@ -2188,13 +2147,13 @@
         <v>8</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2202,10 +2161,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>49</v>
@@ -2214,13 +2173,13 @@
         <v>6</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2228,10 +2187,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>54</v>
@@ -2240,13 +2199,13 @@
         <v>5</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2257,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -2300,19 +2259,19 @@
         <v>32</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2320,10 +2279,10 @@
         <v>43</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D2" s="10">
         <v>8</v>
@@ -2332,7 +2291,7 @@
         <v>76</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2340,10 +2299,10 @@
         <v>54</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D3" s="12">
         <v>3</v>
@@ -2352,7 +2311,7 @@
         <v>68</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2360,10 +2319,10 @@
         <v>49</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D4" s="10">
         <v>4</v>
@@ -2372,7 +2331,7 @@
         <v>72</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2380,10 +2339,10 @@
         <v>59</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D5" s="12">
         <v>2</v>
@@ -2392,7 +2351,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2400,7 +2359,7 @@
         <v>69</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>16</v>
@@ -2412,7 +2371,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2422,123 +2381,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FFA29BFE"/>
-  </sheetPr>
-  <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="65" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFE84393"/>
@@ -2556,37 +2398,37 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>15</v>
@@ -2596,8 +2438,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>189</v>
+      <c r="A2" s="15" t="s">
+        <v>173</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>12</v>
@@ -2633,15 +2475,15 @@
         <v>12</v>
       </c>
       <c r="M2" s="10" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>7</v>
@@ -2650,31 +2492,31 @@
         <v>9</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>16</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/samples/Sample_Reddit_Strategy_iSleep_Month2_2026-03-09.xlsx
+++ b/samples/Sample_Reddit_Strategy_iSleep_Month2_2026-03-09.xlsx
@@ -22,13 +22,13 @@
     <t>Reddit Strategy Report — iSleep</t>
   </si>
   <si>
-    <t>Month 2 | Generated by Sally the Reddit Bot | March 9, 2026</t>
+    <t>Month 2 | Generated by George Reddit Bot | March 9, 2026</t>
   </si>
   <si>
     <t>Package</t>
   </si>
   <si>
-    <t>Package B — Authority</t>
+    <t>Package B</t>
   </si>
   <si>
     <t>Keywords Researched</t>
